--- a/data/processed/ontology/tax/predicate_lexicon.xlsx
+++ b/data/processed/ontology/tax/predicate_lexicon.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,48 +503,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRED_KHAI_CHINH_XAC</t>
+          <t>PRED_THONG_BAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>khai chính xác, trung thực, đầy đủ các nội dung trong hồ sơ khai thuế, khoản thu khác</t>
+          <t>thông báo cho người nộp thuế biết số tiền thuế nợ và số ngày chậm nộp.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>khai chính xác, trung thực, đầy đủ các nội dung trong hồ sơ khai thuế, khoản thu khác</t>
+          <t>thông báo cho người nộp thuế biết số tiền thuế nợ và số ngày chậm nộp. | thông báo cho người nộp thuế biết số tiền thuế nợ và số ngày chậm nộp. với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>khai_chinh_xac</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>từng loại thuế</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -554,65 +554,65 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_khai_chinh_xac;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_thay_cum_thong_bao;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRED_THONG_BAO</t>
+          <t>PRED_HOAN_THANH_NGHIA_VU_NOP_THUE_VA_CAC_NGHIA_VU_CO_LIEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>thông báo cho người nộp thuế biết số tiền thuế nợ và số ngày chậm nộp.</t>
+          <t>hoàn thành nghĩa vụ nộp thuế và các nghĩa vụ có liên quan đến hồ sơ thuế trước</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thông báo cho người nộp thuế biết số tiền thuế nợ và số ngày chậm nộp. | thông báo cho người nộp thuế biết số tiền thuế nợ và số ngày chậm nộp. với cơ quan đăng ký kinh doanh</t>
+          <t>hoàn thành nghĩa vụ nộp thuế và các nghĩa vụ có liên quan đến hồ sơ thuế trước</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>hoan_thanh_nghia_vu_nop_thue_va_cac_nghia_vu_co_lien_quan_den_ho_so_thue_truoc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>thực hiện chia doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -627,29 +627,29 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thong_bao;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_hoan_thanh_nghia_vu_nop_thue_va_cac_nghia_vu_co_lien_quan_den_ho_so_thue_truoc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRED_HOAN_THANH_NGHIA_VU_NOP_THUE_VA_CAC_NGHIA_VU_CO_LIEN</t>
+          <t>PRED_GUI_HO_SO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hoàn thành nghĩa vụ nộp thuế và các nghĩa vụ có liên quan đến hồ sơ thuế trước</t>
+          <t>nộp hồ sơ khai thuế</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hoàn thành nghĩa vụ nộp thuế và các nghĩa vụ có liên quan đến hồ sơ thuế trước</t>
+          <t>nộp hồ sơ khai thuế</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hoan_thanh_nghia_vu_nop_thue_va_cac_nghia_vu_co_lien_quan_den_ho_so_thue_truoc</t>
+          <t>gui_ho_so</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>người thành lập doanh nghiệp</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>thực hiện chia doanh nghiệp</t>
+          <t>tháng</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -700,24 +700,24 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_hoan_thanh_nghia_vu_nop_thue_va_cac_nghia_vu_co_lien_quan_den_ho_so_thue_truoc</t>
+          <t>map_khi_thay_cum_gui_ho_so;co_ngoai_le_can_xu_ly_rieng</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRED_CAP_CAC_HO_SO</t>
+          <t>PRED_VAN_PHAI_NOP_HO_SO_KHAI_THUE_THANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cấp các hồ sơ</t>
+          <t>vẫn phải nộp hồ sơ khai thuế tháng</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cấp các hồ sơ</t>
+          <t>vẫn phải nộp hồ sơ khai thuế tháng</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>cap_cac_ho_so</t>
+          <t>van_phai_nop_ho_so_khai_thue_thang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -768,48 +768,52 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_cac_ho_so</t>
+          <t>map_khi_thay_cum_van_phai_nop_ho_so_khai_thue_thang;co_ngoai_le_can_xu_ly_rieng</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRED_NEU_QUYEN_SO_HUU</t>
+          <t>PRED_DANG_KY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nếu quyền sở hữu, quyền sử dụng tài sản</t>
+          <t>đăng ký tạm ngừng hoạt động</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nếu quyền sở hữu, quyền sử dụng tài sản</t>
+          <t>đăng ký tạm ngừng hoạt động | đăng ký tạm ngừng hoạt động với cơ quan thuế</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>neu_quyen_so_huu</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
+          <t>cơ quan thuế</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cơ quan thuế</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>khong</t>
@@ -832,24 +836,24 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_dang_ky;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRED_VAN_PHAI_NOP_HO_SO_KHAI_THUE_THANG</t>
+          <t>PRED_THANH_PHAN_HO_SO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vẫn phải nộp hồ sơ khai thuế tháng</t>
+          <t>thành phần hồ sơ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>vẫn phải nộp hồ sơ khai thuế tháng</t>
+          <t>thành phần hồ sơ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -859,7 +863,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>van_phai_nop_ho_so_khai_thue_thang</t>
+          <t>thanh_phan_ho_so</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -869,7 +873,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -885,12 +889,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -900,24 +904,24 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_van_phai_nop_ho_so_khai_thue_thang;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_thay_cum_thanh_phan_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRED_GUI_HO_SO</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nộp hồ sơ khai thuế tháng</t>
+          <t>kèm theo Nghị định này.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nộp hồ sơ khai thuế tháng</t>
+          <t>kèm theo Nghị định này.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -927,7 +931,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>gui_ho_so</t>
+          <t>kem_theo_nghi_dinh_nay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -937,14 +941,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ho_so</t>
-        </is>
-      </c>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
@@ -953,12 +953,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -968,56 +968,52 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_ho_so;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY</t>
+          <t>PRED_KEM_THEO_BANG_XAC_DINH_SO_THUE_PHAI_NOP_CHO_TUNG_DIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>đăng ký tạm ngừng hoạt động, kinh doanh</t>
+          <t>kèm theo Bảng xác định số thuế phải nộp cho từng địa phương nơi có công ty khai thác than đóng trụ sở theo quy định của Bộ trưởng Bộ Tài chính.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>đăng ký tạm ngừng hoạt động, kinh doanh | đăng ký tạm ngừng hoạt động, kinh doanh với cơ quan thuế</t>
+          <t>kèm theo Bảng xác định số thuế phải nộp cho từng địa phương nơi có công ty khai thác than đóng trụ sở theo quy định của Bộ trưởng Bộ Tài chính.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>kem_theo_bang_xac_dinh_so_thue_phai_nop_cho_tung_dia_phuong_noi_co_cong_ty_khai_thac_than_dong_tru_so_theo_quy_dinh_cua_bo_truong_bo_tai_chinh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>cơ quan thuế</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>cơ quan thuế đã có Thông báo về việc người nộp thuế không hoạt động tại địa chỉ đã đăng ký</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
+          <t>thuế bảo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1025,7 +1021,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1040,39 +1036,39 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PRED_NEU_CO_THEO_DUNG_MAU_QUY_DINH_CUA_BO_TRUONG_BO_TAI_C</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_CHO_NGUOI_KHAI_THUE_HOAC_NGUO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nếu có) theo đúng mẫu quy định của Bộ trưởng Bộ Tài chính</t>
+          <t>kèm theo Nghị định này cho người khai thuế hoặc người được người khai thuế ủy quyền, người bảo lãnh, người nộp thuế thay cho người khai thuế về căn cứ pháp lý ấn định thuế, phương pháp tính thuế, số tiền thuế ấn định chi tiết theo từng loại thuế, t</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nếu có) theo đúng mẫu quy định của Bộ trưởng Bộ Tài chính</t>
+          <t>kèm theo Nghị định này cho người khai thuế hoặc người được người khai thuế ủy quyền, người bảo lãnh, người nộp thuế thay cho người khai thuế về căn cứ pháp lý ấn định thuế, phương pháp tính thuế, số tiền thuế ấn định chi tiết theo từng loại thuế, t</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>neu_co_theo_dung_mau_quy_dinh_cua_bo_truong_bo_tai_chinh</t>
+          <t>kem_theo_nghi_dinh_nay_cho_nguoi_khai_thue_hoac_nguoi_duoc_nguoi_khai_thue_uy_quyen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1080,11 +1076,7 @@
           <t>người thành lập doanh nghiệp</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>quy định của pháp luật có liên quan</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -1093,7 +1085,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1108,52 +1100,52 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRED_THANH_PHAN_HO_SO</t>
+          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>thành phần hồ sơ</t>
+          <t>cấp giấy chứng nhận đăng ký kinh doanh cho cá nhân</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>thành phần hồ sơ</t>
+          <t>cấp giấy chứng nhận đăng ký kinh doanh cho cá nhân | cấp giấy chứng nhận đăng ký kinh doanh cho cá nhân với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>thanh_phan_ho_so</t>
+          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ho_so</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1161,7 +1153,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1176,24 +1168,24 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thanh_phan_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
+          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY</t>
+          <t>PRED_KEM_THEO_THU_BAO_LANH_CUA_TO_CHUC_TIN_DUNG_DOI_VOI_S</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này.</t>
+          <t>kèm theo thư bảo lãnh của tổ chức tín dụng đối với số tiền thuế, tiền chậm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này.</t>
+          <t>kèm theo thư bảo lãnh của tổ chức tín dụng đối với số tiền thuế, tiền chậm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1203,7 +1195,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>kem_theo_nghi_dinh_nay</t>
+          <t>kem_theo_thu_bao_lanh_cua_to_chuc_tin_dung_doi_voi_so_tien_thue</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1213,10 +1205,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>người thành lập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hải quan</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -1247,32 +1243,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PRED_CAP_DICH_VU_DUOC_XAC_DINH</t>
+          <t>PRED_GUI_DEN_NGUOI_NOP_THUE_BI_CUONG_CHE_VA_CO_QUAN_QUAN_</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cấp dịch vụ được xác định</t>
+          <t>gửi đến người nộp thuế bị cưỡng chế và cơ quan quản lý nhà nước có thẩm quyền để thu hồi giấy chứng nhận</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cấp dịch vụ được xác định</t>
+          <t>gửi đến người nộp thuế bị cưỡng chế và cơ quan quản lý nhà nước có thẩm quyền để thu hồi giấy chứng nhận</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>cap_dich_vu_duoc_xac_dinh</t>
+          <t>gui_den_nguoi_nop_thue_bi_cuong_che_va_co_quan_quan_ly_nha_nuoc_co_tham_quyen_de_thu_hoi_giay_chung_nhan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1280,15 +1276,11 @@
           <t>người thành lập doanh nghiệp</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>thuế giá</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1303,56 +1295,52 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_dich_vu_duoc_xac_dinh</t>
+          <t>map_khi_thay_cum_gui_den_nguoi_nop_thue_bi_cuong_che_va_co_quan_quan_ly_nha_nuoc_co_tham_quyen_de_thu_hoi_giay_chung_nhan;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PRED_NEU_CO_TONG_DOANH_THU_BAN_HANG_HOA_VA_CUNG</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_SO_151_2017_ND_CP_NGAY_26_THANG_1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nếu có tổng doanh thu bán hàng hoá và cung</t>
+          <t>kèm theo Nghị định số 151/2017/NĐ-CP ngày 26 tháng 12 năm 2017 của Chính phủ quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nếu có tổng doanh thu bán hàng hoá và cung</t>
+          <t>kèm theo Nghị định số 151/2017/NĐ-CP ngày 26 tháng 12 năm 2017 của Chính phủ quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>neu_co_tong_doanh_thu_ban_hang_hoa_va_cung</t>
+          <t>kem_theo_nghi_dinh_so_151_2017_nd_cp_ngay_26_thang_12_nam_2017_cua_chinh_phu_quy_dinh_chi_tiet_mot_so_dieu_cua_luat_quan_ly</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>thuế giá</t>
-        </is>
-      </c>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
@@ -1361,7 +1349,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1371,53 +1359,57 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PRED_NEU_DU_DIEU_KIEN_KHAI_THUE_GIA_TRI_GIA_TANG_THEO_QUY</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_QUA_CONG_THONG_TIN_DIEN_TU_CU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nếu đủ điều kiện khai thuế giá trị gia tăng theo quý thì</t>
+          <t>kèm theo Nghị định này qua Cổng thông tin điện tử của Tổng cục Thuế hoặc qua tổ chức cung</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nếu đủ điều kiện khai thuế giá trị gia tăng theo quý thì</t>
+          <t>kèm theo Nghị định này qua Cổng thông tin điện tử của Tổng cục Thuế hoặc qua tổ chức cung | kèm theo Nghị định này qua Cổng thông tin điện tử của Tổng cục Thuế hoặc qua tổ chức cung với cơ quan thuế</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>neu_du_dieu_kien_khai_thue_gia_tri_gia_tang_theo_quy_thi</t>
+          <t>kem_theo_nghi_dinh_nay_qua_cong_thong_tin_dien_tu_cua_tong_cuc_thue_hoac_qua_to_chuc_cung</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>cơ quan thuế</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1425,12 +1417,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1440,48 +1432,56 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY_VA_PHAI_TINH_TIEN_CHAM_NOP_TH</t>
+          <t>PRED_NEU_THUOC_DOI_TUONG_CHUYEN_SANG_SU_DUNG_HOA_DON_DIEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này và phải tính tiền chậm nộp theo quy định.</t>
+          <t>nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này và phải tính tiền chậm nộp theo quy định.</t>
+          <t>nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. | nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. với cơ quan thuế</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dieu_kien_ap_dung</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>kem_theo_nghi_dinh_nay_va_phai_tinh_tien_cham_nop_theo_quy_dinh</t>
+          <t>neu_thuoc_doi_tuong_chuyen_sang_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_de_dang_ky_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_theo_huong_dan_tai_dieu_nay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dieu_kien</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>này nếu</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>cơ quan thuế</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1499,29 +1499,29 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PRED_KE_KHAI_LAI_HO_SO_KHAI_THUE</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_NEU_THUOC_DOI_TUONG_CHUYEN_SA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kê khai lại hồ sơ khai thuế</t>
+          <t>kèm theo Nghị định này nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kê khai lại hồ sơ khai thuế</t>
+          <t>kèm theo Nghị định này nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. | kèm theo Nghị định này nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. với cơ quan thuế</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ke_khai_lai_ho_so_khai_thue</t>
+          <t>kem_theo_nghi_dinh_nay_neu_thuoc_doi_tuong_chuyen_sang_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_de_dang_ky_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_theo_huong_dan_tai_dieu_nay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1541,15 +1541,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>không phát sinh thay đổi tăng</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>này nếu</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>cơ quan thuế</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1557,12 +1561,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1572,52 +1576,56 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_ke_khai_lai_ho_so_khai_thue;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRED_NEU_KHONG_PHAT_SINH_THAY_DOI_TANG</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_CUNG_THOI_HAN_NOP_HO_SO_KHAI_</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nếu không phát sinh thay đổi tăng, giảm diện tích chịu thuế sử dụng đất nông nghiệp.</t>
+          <t>kèm theo Nghị định này cùng thời hạn nộp hồ sơ khai thuế giá trị gia tăng áp dụng</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nếu không phát sinh thay đổi tăng, giảm diện tích chịu thuế sử dụng đất nông nghiệp.</t>
+          <t>kèm theo Nghị định này cùng thời hạn nộp hồ sơ khai thuế giá trị gia tăng áp dụng | kèm theo Nghị định này cùng thời hạn nộp hồ sơ khai thuế giá trị gia tăng áp dụng với cơ quan thuế</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>neu_khong_phat_sinh_thay_doi_tang</t>
+          <t>kem_theo_nghi_dinh_nay_cung_thoi_han_nop_ho_so_khai_thue_gia_tri_gia_tang_ap_dung</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>không phát sinh thay đổi tăng</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>trị gia</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>cơ quan thuế</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1625,12 +1633,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1640,24 +1648,24 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_BANG_XAC_DINH_SO_THUE_PHAI_NOP_CHO_TUNG_DIA</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_TRUONG_HOP_TRONG_KY_KHONG_SU_</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kèm theo Bảng xác định số thuế phải nộp cho từng địa phương nơi có công ty khai thác than đóng trụ sở theo quy định của Bộ trưởng Bộ Tài chính.</t>
+          <t>kèm theo Nghị định này. Trường hợp trong kỳ không sử dụng hóa đơn thì doanh nghiệp, tổ chức kinh tế, hộ, cá nhân kinh doanh nộp báo cáo tình hình sử dụng hóa đơn ghi số lượng hóa đơn sử dụng bằng không (= 0), không cần gửi bảng kê hóa đơn sử dụng trong kỳ. Trường hợp kỳ trước</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kèm theo Bảng xác định số thuế phải nộp cho từng địa phương nơi có công ty khai thác than đóng trụ sở theo quy định của Bộ trưởng Bộ Tài chính.</t>
+          <t>kèm theo Nghị định này. Trường hợp trong kỳ không sử dụng hóa đơn thì doanh nghiệp, tổ chức kinh tế, hộ, cá nhân kinh doanh nộp báo cáo tình hình sử dụng hóa đơn ghi số lượng hóa đơn sử dụng bằng không (= 0), không cần gửi bảng kê hóa đơn sử dụng trong kỳ. Trường hợp kỳ trước</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1667,7 +1675,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>kem_theo_bang_xac_dinh_so_thue_phai_nop_cho_tung_dia_phuong_noi_co_cong_ty_khai_thac_than_dong_tru_so_theo_quy_dinh_cua_bo_truong_bo_tai_chinh</t>
+          <t>kem_theo_nghi_dinh_nay_truong_hop_trong_ky_khong_su_dung_hoa_don_thi_doanh_nghiep</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1677,15 +1685,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan thuế</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>thuế bảo</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>báo cáo</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>cơ quan thuế</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1715,17 +1727,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PRED_NOP_THEO_HO_SO_KHAI_THUE_CUA_NGUOI_NOP_THUE</t>
+          <t>PRED_KEM_THEO_BIEN_LAI_MAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nộp theo hồ sơ khai thuế của người nộp thuế</t>
+          <t>kèm theo biên lai mẫu)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nộp theo hồ sơ khai thuế của người nộp thuế | nộp theo hồ sơ khai thuế của người nộp thuế với cơ quan thuế</t>
+          <t>kèm theo biên lai mẫu)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1735,7 +1747,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>nop_theo_ho_so_khai_thue_cua_nguoi_nop_thue</t>
+          <t>kem_theo_bien_lai_mau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1748,16 +1760,8 @@
           <t>người thành lập doanh nghiệp</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>nộp theo</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1765,7 +1769,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1780,24 +1784,24 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_nop_theo_ho_so_khai_thue_cua_nguoi_nop_thue</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY_CHO_NGUOI_KHAI_THUE_HOAC_NGUO</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_CUNG_VOI_VIEC_NOP_TO_KHAI_THU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này cho người khai thuế hoặc người được người khai thuế ủy quyền, người bảo lãnh, người nộp thuế thay cho người khai thuế về căn cứ pháp lý ấn định thuế, phương pháp tính thuế, số tiền thuế ấn định chi tiết theo từng loại thuế, t</t>
+          <t>kèm theo Nghị định này cùng với việc nộp tờ khai thuế giá trị gia tăng.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này cho người khai thuế hoặc người được người khai thuế ủy quyền, người bảo lãnh, người nộp thuế thay cho người khai thuế về căn cứ pháp lý ấn định thuế, phương pháp tính thuế, số tiền thuế ấn định chi tiết theo từng loại thuế, t</t>
+          <t>kèm theo Nghị định này cùng với việc nộp tờ khai thuế giá trị gia tăng.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1807,7 +1811,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>kem_theo_nghi_dinh_nay_cho_nguoi_khai_thue_hoac_nguoi_duoc_nguoi_khai_thue_uy_quyen</t>
+          <t>kem_theo_nghi_dinh_nay_cung_voi_viec_nop_to_khai_thue_gia_tri_gia_tang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1817,10 +1821,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>của cơ</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
@@ -1851,45 +1859,45 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_DOANH_THU_DE_TINH_THU_NHAP_CHIU_THUE_DUOC_PHAN_BO_DE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cấp giấy chứng nhận đăng ký kinh doanh cho cá nhân</t>
+          <t>doanh thu để tính thu nhập chịu thuế được phân bổ đều cho số năm trả tiền trước hoặc xác định theo doanh thu trả tiền một lần.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cấp giấy chứng nhận đăng ký kinh doanh cho cá nhân | cấp giấy chứng nhận đăng ký kinh doanh cho cá nhân với cơ quan đăng ký kinh doanh</t>
+          <t>doanh thu để tính thu nhập chịu thuế được phân bổ đều cho số năm trả tiền trước hoặc xác định theo doanh thu trả tiền một lần.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>doanh_thu_de_tinh_thu_nhap_chiu_thue_duoc_phan_bo_deu_cho_so_nam_tra_tien_truoc_hoac_xac_dinh_theo_doanh_thu_tra_tien_mot_lan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Trường hợp doanh nghiệp đang trong thời gian hưởng ưu đãi thuế thu nhập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>khong</t>
@@ -1912,24 +1920,24 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>map_khi_thay_cum_doanh_thu_de_tinh_thu_nhap_chiu_thue_duoc_phan_bo_deu_cho_so_nam_tra_tien_truoc_hoac_xac_dinh_theo_doanh_thu_tra_tien_mot_lan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_THU_BAO_LANH_CUA_TO_CHUC_TIN_DUNG_DOI_VOI_S</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_VA_NGUNG_TIEP_NHAN_HOA_DON_DI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>kèm theo thư bảo lãnh của tổ chức tín dụng đối với số tiền thuế, tiền chậm</t>
+          <t>kèm theo Nghị định này) và ngừng tiếp nhận hóa đơn điện tử, ngừng tiếp nhận hóa đơn điện tử khởi tạo từ máy tính tiền đối với người</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kèm theo thư bảo lãnh của tổ chức tín dụng đối với số tiền thuế, tiền chậm</t>
+          <t>kèm theo Nghị định này) và ngừng tiếp nhận hóa đơn điện tử, ngừng tiếp nhận hóa đơn điện tử khởi tạo từ máy tính tiền đối với người</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1939,7 +1947,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>kem_theo_thu_bao_lanh_cua_to_chuc_tin_dung_doi_voi_so_tien_thue</t>
+          <t>kem_theo_nghi_dinh_nay_va_ngung_tiep_nhan_hoa_don_dien_tu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1952,11 +1960,7 @@
           <t>người thành lập doanh nghiệp</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>hải quan</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -1975,7 +1979,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1987,17 +1991,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRED_GUI_DEN_NGUOI_NOP_THUE_BI_CUONG_CHE_VA_CO_QUAN_QUAN_</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_DE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gửi đến người nộp thuế bị cưỡng chế và cơ quan quản lý nhà nước có thẩm quyền để thu hồi giấy chứng nhận</t>
+          <t>kèm theo Nghị định này để</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>gửi đến người nộp thuế bị cưỡng chế và cơ quan quản lý nhà nước có thẩm quyền để thu hồi giấy chứng nhận</t>
+          <t>kèm theo Nghị định này để</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2007,29 +2011,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>gui_den_nguoi_nop_thue_bi_cuong_che_va_co_quan_quan_ly_nha_nuoc_co_tham_quyen_de_thu_hoi_giay_chung_nhan</t>
+          <t>kem_theo_nghi_dinh_nay_de</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ban hành</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2044,52 +2052,52 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_den_nguoi_nop_thue_bi_cuong_che_va_co_quan_quan_ly_nha_nuoc_co_tham_quyen_de_thu_hoi_giay_chung_nhan;thuong_di_kem_thoi_han</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRED_BI_HUY_BO_TRONG_CAC</t>
+          <t>PRED_KEM_THEO_NGHI_DINH_NAY_DE_GUI_CO_QUAN_QUAN_LY_THUE_C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bị hủy bỏ trong các</t>
+          <t>kèm theo Nghị định này để gửi cơ quan quản lý thuế cùng với thời gian gửi Tờ khai phí, lệ phí (trừ phí hải quan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bị hủy bỏ trong các | bị hủy bỏ trong các với cơ quan thuế</t>
+          <t>kèm theo Nghị định này để gửi cơ quan quản lý thuế cùng với thời gian gửi Tờ khai phí, lệ phí (trừ phí hải quan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>bi_huy_bo_trong_cac</t>
+          <t>kem_theo_nghi_dinh_nay_de_gui_co_quan_quan_ly_thue_cung_voi_thoi_gian_gui_to_khai_phi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ban hành</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>khong</t>
@@ -2097,7 +2105,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2112,24 +2120,24 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_bi_huy_bo_trong_cac</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_SO_151_2017_ND_CP_NGAY_26_THANG_1</t>
+          <t>PRED_KEM_THEO_THONG_TU_NAY_DE_SU_DUNG_THU_THUE_SU_DUNG_DA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định số 151/2017/NĐ-CP ngày 26 tháng 12 năm 2017 của Chính phủ quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản</t>
+          <t>kèm theo Thông tư này để sử dụng thu thuế sử dụng đất nông nghiệp, thuế sử dụng đất phi nông nghiệp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định số 151/2017/NĐ-CP ngày 26 tháng 12 năm 2017 của Chính phủ quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản</t>
+          <t>kèm theo Thông tư này để sử dụng thu thuế sử dụng đất nông nghiệp, thuế sử dụng đất phi nông nghiệp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2139,7 +2147,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>kem_theo_nghi_dinh_so_151_2017_nd_cp_ngay_26_thang_12_nam_2017_cua_chinh_phu_quy_dinh_chi_tiet_mot_so_dieu_cua_luat_quan_ly</t>
+          <t>kem_theo_thong_tu_nay_de_su_dung_thu_thue_su_dung_dat_nong_nghiep</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2171,7 +2179,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2183,17 +2191,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_BO_HO_SO_VE_NGUON_GOC_TAI_SAN</t>
+          <t>PRED_KEM_THEO_BAN_HANG_HOA_NHU_DICH_VU_DAO_TAO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kèm theo bộ hồ sơ về nguồn gốc tài sản.</t>
+          <t>kèm theo bán hàng hóa như dịch vụ đào tạo, bảo dưỡng, chuyển giao công nghệ kèm theo bán sản phẩm.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kèm theo bộ hồ sơ về nguồn gốc tài sản.</t>
+          <t>kèm theo bán hàng hóa như dịch vụ đào tạo, bảo dưỡng, chuyển giao công nghệ kèm theo bán sản phẩm.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2203,7 +2211,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>kem_theo_bo_ho_so_ve_nguon_goc_tai_san</t>
+          <t>kem_theo_ban_hang_hoa_nhu_dich_vu_dao_tao</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2216,11 +2224,7 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>lập hóa</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
@@ -2239,7 +2243,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2251,17 +2255,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PRED_NEU_THUOC_DOI_TUONG_CHUYEN_SANG_SU_DUNG_HOA_DON_DIEN</t>
+          <t>PRED_NEU_CO_KHO_KHAN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này.</t>
+          <t>nếu có khó khăn, vướng mắc, đề nghị các đơn vị, cơ sở kinh doanh phản ánh kịp thời về Bộ Tài chính để được giải quyết./</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. | nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. với cơ quan thuế</t>
+          <t>nếu có khó khăn, vướng mắc, đề nghị các đơn vị, cơ sở kinh doanh phản ánh kịp thời về Bộ Tài chính để được giải quyết./</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2271,7 +2275,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>neu_thuoc_doi_tuong_chuyen_sang_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_de_dang_ky_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_theo_huong_dan_tai_dieu_nay</t>
+          <t>neu_co_kho_khan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2284,16 +2288,8 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>này nếu</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>khong</t>
@@ -2311,7 +2307,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2323,17 +2319,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY_NEU_THUOC_DOI_TUONG_CHUYEN_SA</t>
+          <t>PRED_KEM_THEO_THONG_TU_SO_69_2025_TT_BTC_NGAY_01_THANG_7_</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này.</t>
+          <t>Kèm theo Thông tư số 69/2025/TT-BTC ngày 01 tháng 7 năm 2025 của Bộ trưởng Bộ Tài chính) STT Danh mục nhóm hàng hóa, dịch vụ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kèm theo Nghị định này nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. | kèm theo Nghị định này nếu thuộc đối tượng chuyển sang sử dụng hóa đơn điện tử có mã của cơ quan thuế để đăng ký sử dụng hóa đơn điện tử có mã của cơ quan thuế theo hướng dẫn tại Điều này. với cơ quan thuế</t>
+          <t>Kèm theo Thông tư số 69/2025/TT-BTC ngày 01 tháng 7 năm 2025 của Bộ trưởng Bộ Tài chính) STT Danh mục nhóm hàng hóa, dịch vụ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2343,7 +2339,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>kem_theo_nghi_dinh_nay_neu_thuoc_doi_tuong_chuyen_sang_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_de_dang_ky_su_dung_hoa_don_dien_tu_co_ma_cua_co_quan_thue_theo_huong_dan_tai_dieu_nay</t>
+          <t>kem_theo_thong_tu_so_69_2025_tt_btc_ngay_01_thang_7_nam_2025_cua_bo_truong_bo_tai_chinh_stt_danh_muc_nhom_hang_hoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2356,16 +2352,8 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>này nếu</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>khong</t>
@@ -2383,556 +2371,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY_CUNG_THOI_HAN_NOP_HO_SO_KHAI_</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>kèm theo Nghị định này cùng thời hạn nộp hồ sơ khai thuế giá trị gia tăng áp dụng</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>kèm theo Nghị định này cùng thời hạn nộp hồ sơ khai thuế giá trị gia tăng áp dụng | kèm theo Nghị định này cùng thời hạn nộp hồ sơ khai thuế giá trị gia tăng áp dụng với cơ quan thuế</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>kem_theo_nghi_dinh_nay_cung_thoi_han_nop_ho_so_khai_thue_gia_tri_gia_tang_ap_dung</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>trị gia</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY_TRUONG_HOP_TRONG_KY_KHONG_SU_</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>kèm theo Nghị định này. Trường hợp trong kỳ không sử dụng hóa đơn thì doanh nghiệp, tổ chức kinh tế, hộ, cá nhân kinh doanh nộp báo cáo tình hình sử dụng hóa đơn ghi số lượng hóa đơn sử dụng bằng không (= 0), không cần gửi bảng kê hóa đơn sử dụng trong kỳ. Trường hợp kỳ trước</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>kèm theo Nghị định này. Trường hợp trong kỳ không sử dụng hóa đơn thì doanh nghiệp, tổ chức kinh tế, hộ, cá nhân kinh doanh nộp báo cáo tình hình sử dụng hóa đơn ghi số lượng hóa đơn sử dụng bằng không (= 0), không cần gửi bảng kê hóa đơn sử dụng trong kỳ. Trường hợp kỳ trước</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>kem_theo_nghi_dinh_nay_truong_hop_trong_ky_khong_su_dung_hoa_don_thi_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>báo cáo</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>cơ quan thuế</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PRED_KEM_THEO_BIEN_LAI_MAU</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>kèm theo biên lai mẫu)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>kèm theo biên lai mẫu)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>kem_theo_bien_lai_mau</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PRED_KEM_THEO_NGHI_DINH_NAY_CUNG_VOI_VIEC_NOP_TO_KHAI_THU</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>kèm theo Nghị định này cùng với việc nộp tờ khai thuế giá trị gia tăng.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>kèm theo Nghị định này cùng với việc nộp tờ khai thuế giá trị gia tăng.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>kem_theo_nghi_dinh_nay_cung_voi_viec_nop_to_khai_thue_gia_tri_gia_tang</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>của cơ</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>PRED_NEU_VIEC_KHAI_THUE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>nếu việc khai thuế</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>nếu việc khai thuế</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>neu_viec_khai_thue</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>dieu_kien</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>người thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>phải nộp hoặc chỉ làm tăng hoặc giảm số thuế giá trị gia tăng còn được khấu trừ chuyển sang tháng</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PRED_CHIA_TU_HOAT_DONG_GOP_VON</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>chia từ hoạt động góp vốn, mua cổ phần, liên doanh, liên kết với doanh nghiệp trong nước, sau</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>chia từ hoạt động góp vốn, mua cổ phần, liên doanh, liên kết với doanh nghiệp trong nước, sau</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>khac</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>chia_tu_hoat_dong_gop_von</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>von_va_gop_von</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>sau khi</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_chia_tu_hoat_dong_gop_von</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>PRED_DOANH_THU_DE_TINH_THU_NHAP_CHIU_THUE_DUOC_PHAN_BO_DE</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>doanh thu để tính thu nhập chịu thuế được phân bổ đều cho số năm trả tiền trước hoặc xác định theo doanh thu trả tiền một lần.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>doanh thu để tính thu nhập chịu thuế được phân bổ đều cho số năm trả tiền trước hoặc xác định theo doanh thu trả tiền một lần.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>doanh_thu_de_tinh_thu_nhap_chiu_thue_duoc_phan_bo_deu_cho_so_nam_tra_tien_truoc_hoac_xac_dinh_theo_doanh_thu_tra_tien_mot_lan</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>căn cứ</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_doanh_thu_de_tinh_thu_nhap_chiu_thue_duoc_phan_bo_deu_cho_so_nam_tra_tien_truoc_hoac_xac_dinh_theo_doanh_thu_tra_tien_mot_lan</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PRED_NEU_DOANH_NGHIEP_THUC_HIEN_NHIEU_HOAT_DONG_SAN_XUAT</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>nếu doanh nghiệp thực hiện nhiều hoạt động sản xuất, kinh doanh thì doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>nếu doanh nghiệp thực hiện nhiều hoạt động sản xuất, kinh doanh thì doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>dieu_kien_ap_dung</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>neu_doanh_nghiep_thuc_hien_nhieu_hoat_dong_san_xuat</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>dieu_kien</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
         </is>
       </c>
     </row>
